--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00853B-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00853B-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5DCE3E9-AB69-4471-B298-8DAEE40A3003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8089250A-D0D1-4A8D-A9BD-E91CF6360D0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{C87DDD68-C570-47C5-B69F-FFDD6BC1964C}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{D4E39012-1A49-4DE4-8603-E175BE16B655}"/>
   </bookViews>
   <sheets>
     <sheet name="00853B-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1565,25 +1565,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BB79B38-C636-42BC-8D46-B81CDAABE16C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CA837CA-825B-4DE6-BD8C-725A1A780AF9}">
   <dimension ref="A1:R37"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1611,7 +1611,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1641,7 +1641,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1687,7 +1687,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1737,7 +1737,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1791,7 +1791,7 @@
         <v>4.66</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1903,7 +1903,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>25</v>
       </c>
@@ -1959,7 +1959,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>25</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="39">
         <v>2024</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>4.43</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>25</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>1.1100000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>25</v>
       </c>
@@ -2181,7 +2181,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>25</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>25</v>
       </c>
@@ -2293,7 +2293,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="37">
         <v>2023</v>
       </c>
@@ -2347,7 +2347,7 @@
         <v>4.53</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>25</v>
       </c>
@@ -2403,7 +2403,7 @@
         <v>0.81</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
@@ -2459,7 +2459,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2571,7 +2571,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2022</v>
       </c>
@@ -2625,7 +2625,7 @@
         <v>3.16</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>25</v>
       </c>
@@ -2681,7 +2681,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -2737,7 +2737,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>25</v>
       </c>
@@ -2793,7 +2793,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>25</v>
       </c>
@@ -2849,7 +2849,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <v>2021</v>
       </c>
@@ -2903,7 +2903,7 @@
         <v>2.76</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>25</v>
       </c>
@@ -2959,7 +2959,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>25</v>
       </c>
@@ -3015,7 +3015,7 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>25</v>
       </c>
@@ -3071,7 +3071,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>25</v>
       </c>
@@ -3127,7 +3127,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="39">
         <v>2020</v>
       </c>
@@ -3181,7 +3181,7 @@
         <v>3.24</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
         <v>25</v>
       </c>
@@ -3237,7 +3237,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>25</v>
       </c>
@@ -3293,7 +3293,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
         <v>25</v>
       </c>
@@ -3349,7 +3349,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
         <v>25</v>
       </c>
@@ -3405,7 +3405,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="37">
         <v>2019</v>
       </c>
@@ -3459,7 +3459,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>25</v>
       </c>
@@ -3515,7 +3515,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="39" t="s">
         <v>74</v>
       </c>
